--- a/排期工具_维护手册.xlsx
+++ b/排期工具_维护手册.xlsx
@@ -7,7 +7,8 @@
     <sheet name="常见情况" sheetId="2" r:id="rId2"/>
     <sheet name="问AI模板" sheetId="3" r:id="rId3"/>
     <sheet name="出问题了" sheetId="4" r:id="rId4"/>
-    <sheet name="包里有什么" sheetId="5" r:id="rId5"/>
+    <sheet name="表单该有哪些列" sheetId="5" r:id="rId5"/>
+    <sheet name="包里有什么" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -37,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -140,8 +141,30 @@
       <name val="微软雅黑"/>
       <color rgb="6A6A7A"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <b/>
+      <color rgb="2C2C2A"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <b/>
+      <color rgb="2C2C2A"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <color rgb="1B5E3A"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <color rgb="1B4374"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="16">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -218,8 +241,26 @@
         <bgColor/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F5FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF1FB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -459,11 +500,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="D8DAE5"/>
+      </left>
+      <right style="thin">
+        <color rgb="D8DAE5"/>
+      </right>
+      <top style="thin">
+        <color rgb="D8DAE5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="D8DAE5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="D8DAE5"/>
+      </left>
+      <right style="thin">
+        <color rgb="D8DAE5"/>
+      </right>
+      <top style="thin">
+        <color rgb="D8DAE5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="D8DAE5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="D8DAE5"/>
+      </left>
+      <right style="thin">
+        <color rgb="D8DAE5"/>
+      </right>
+      <top style="thin">
+        <color rgb="D8DAE5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="D8DAE5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="D8DAE5"/>
+      </left>
+      <right style="thin">
+        <color rgb="D8DAE5"/>
+      </right>
+      <top style="thin">
+        <color rgb="D8DAE5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="D8DAE5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -516,6 +617,18 @@
       <alignment horizontal="left" vertical="top" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -1481,7 +1594,307 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C27"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="62.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="3" t="str">
+        <v>需求收集表该有哪些列</v>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="4" t="str">
+        <v>这是系统能认出来的全部列。改需求收集表之前对一遍，避免加了列系统读不到。表头分两行：上面一行写「组名」（合并单元格），下面一行写「列名」。</v>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="5" t="str">
+        <v>组名（表头第一行）</v>
+      </c>
+      <c r="B4" s="5" t="str">
+        <v>列名（表头第二行）</v>
+      </c>
+      <c r="C4" s="5" t="str">
+        <v>单元格里填什么</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="20" t="str">
+        <v>（不需要组名）</v>
+      </c>
+      <c r="B5" s="6" t="str">
+        <v>需求名</v>
+      </c>
+      <c r="C5" s="7" t="str">
+        <v>需求的名字。也可以写成「需求名称」「需求标题」</v>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1" xml:space="preserve">
+      <c r="A6" s="20" t="str">
+        <v/>
+      </c>
+      <c r="B6" s="6" t="str">
+        <v>DDL</v>
+      </c>
+      <c r="C6" s="7" t="str" xml:space="preserve">
+        <v xml:space="preserve">日期。写「2026年11月13日」「2026/11/13」都认。
+也可以写成「截止日期」「期望完成时间」「交付时间」</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="20" t="str">
+        <v/>
+      </c>
+      <c r="B7" s="6" t="str">
+        <v>提需人</v>
+      </c>
+      <c r="C7" s="7" t="str">
+        <v>谁提的。也可以写成「提单人」「需求方」「提出人」</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="20" t="str">
+        <v/>
+      </c>
+      <c r="B8" s="6" t="str">
+        <v>需求描述</v>
+      </c>
+      <c r="C8" s="7" t="str">
+        <v>补充说明，可留空。也可以写成「备注」「补充说明」</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="20" t="str">
+        <v/>
+      </c>
+      <c r="B9" s="6" t="str">
+        <v>是否需要添加需求副本</v>
+      </c>
+      <c r="C9" s="7" t="str">
+        <v>填「是」表示这条需求要拆成多份</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="20" t="str">
+        <v/>
+      </c>
+      <c r="B10" s="6" t="str">
+        <v>需求副本信息</v>
+      </c>
+      <c r="C10" s="7" t="str">
+        <v>副本的名字和各自的 DDL</v>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1" xml:space="preserve">
+      <c r="A11" s="21" t="str" xml:space="preserve">
+        <v xml:space="preserve">需求类型
+（组名含「需求类型」
+「需求分类」「需求大类」都认）</v>
+      </c>
+      <c r="B11" s="8" t="str">
+        <v>场景类</v>
+      </c>
+      <c r="C11" s="9" t="str" xml:space="preserve">
+        <v xml:space="preserve">剧情场景　或　世界观场景
+（也接受写「剧情」「世界观」这种简写）</v>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1" xml:space="preserve">
+      <c r="A12" s="21" t="str">
+        <v/>
+      </c>
+      <c r="B12" s="8" t="str">
+        <v>角色类</v>
+      </c>
+      <c r="C12" s="9" t="str" xml:space="preserve">
+        <v xml:space="preserve">重点NPC　或　NPC
+（也接受写「重点角色」「关键NPC」「普通NPC」）</v>
+      </c>
+    </row>
+    <row r="13" ht="38" customHeight="1" xml:space="preserve">
+      <c r="A13" s="21" t="str">
+        <v/>
+      </c>
+      <c r="B13" s="8" t="str">
+        <v>纯文学类</v>
+      </c>
+      <c r="C13" s="9" t="str" xml:space="preserve">
+        <v xml:space="preserve">简单补充设定　或　系统文学设定
+（也接受写「补充设定」「系统概念设定」「系统设定」）</v>
+      </c>
+    </row>
+    <row r="14" ht="68" customHeight="1" xml:space="preserve">
+      <c r="A14" s="20" t="str" xml:space="preserve">
+        <v xml:space="preserve">需求应用与露出
+（组名含「应用与露出」
+「需求应用」「露出管线」都认）</v>
+      </c>
+      <c r="B14" s="6" t="str">
+        <v>局内（列名可自定）</v>
+      </c>
+      <c r="C14" s="7" t="str" xml:space="preserve">
+        <v xml:space="preserve">填管线名，多个用逗号分隔。九条管线：
+英雄线　战场玩法线　系统线　Bible概念　区域概念
+叙事　站点　CG　PV
+前面加「世界观」也认，如「世界观Bible概念」</v>
+      </c>
+    </row>
+    <row r="15" ht="53" customHeight="1" xml:space="preserve">
+      <c r="A15" s="21" t="str" xml:space="preserve">
+        <v xml:space="preserve">已有产出：文学
+（组名含「已有产出」
+「现有产出」「已有资产」都认）</v>
+      </c>
+      <c r="B15" s="8" t="str">
+        <v>Bible设定</v>
+      </c>
+      <c r="C15" s="9" t="str" xml:space="preserve">
+        <v xml:space="preserve">世界特点总述　天文地理设定　世界危机与矛盾　历法节日
+文明设定（与关系）　生态设定　种族设定　国家设定
+科技设定　世界学术设定　世界宗教设定　势力设定</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="21" t="str">
+        <v/>
+      </c>
+      <c r="B16" s="8" t="str">
+        <v>叙事设计</v>
+      </c>
+      <c r="C16" s="9" t="str">
+        <v>年度叙事物料框架搭建　年度事件　剧情设计</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="21" t="str">
+        <v/>
+      </c>
+      <c r="B17" s="8" t="str">
+        <v>物料应用</v>
+      </c>
+      <c r="C17" s="9" t="str">
+        <v>细分区域设定　场景设定　道具设定</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="21" t="str">
+        <v/>
+      </c>
+      <c r="B18" s="8" t="str">
+        <v>角色设定</v>
+      </c>
+      <c r="C18" s="9" t="str">
+        <v>NPC角色卡　重点NPC角色卡　英雄角色卡</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="20" t="str">
+        <v>已有产出：美术</v>
+      </c>
+      <c r="B19" s="6" t="str">
+        <v>角色原画</v>
+      </c>
+      <c r="C19" s="7" t="str">
+        <v>印象图　设定图　三视图　线条稿</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="20" t="str">
+        <v/>
+      </c>
+      <c r="B20" s="6" t="str">
+        <v>场景原画</v>
+      </c>
+      <c r="C20" s="7" t="str">
+        <v>概念方向草图　概念图　设定与拆分图　场景美宣图</v>
+      </c>
+    </row>
+    <row r="21" ht="68" customHeight="1" xml:space="preserve">
+      <c r="A21" s="21" t="str" xml:space="preserve">
+        <v xml:space="preserve">特殊产出需求
+（组名含「特殊产出」
+「选做产出」「额外产出」都认）</v>
+      </c>
+      <c r="B21" s="8" t="str">
+        <v>Bible设定需求</v>
+      </c>
+      <c r="C21" s="9" t="str" xml:space="preserve">
+        <v xml:space="preserve">和上面「已有产出」的可填内容完全一样。
+区别只在组名：写在「已有产出」下 = 已经有了；
+写在「特殊产出需求」下 = 这次要新做。
+列名带不带「需求」后缀都认。</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="21" t="str">
+        <v/>
+      </c>
+      <c r="B22" s="8" t="str">
+        <v>场景原画需求</v>
+      </c>
+      <c r="C22" s="9" t="str">
+        <v>同上</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="21" t="str">
+        <v/>
+      </c>
+      <c r="B23" s="8" t="str">
+        <v>角色设定需求</v>
+      </c>
+      <c r="C23" s="9" t="str">
+        <v>同上</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="21" t="str">
+        <v/>
+      </c>
+      <c r="B24" s="8" t="str">
+        <v>物料应用需求</v>
+      </c>
+      <c r="C24" s="9" t="str">
+        <v>同上</v>
+      </c>
+    </row>
+    <row r="25" ht="8" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="22" t="str">
+        <v>单元格里写「√」「是」「有」也认，表示这一整类都有。留空 / 写「无」「否」「/」表示没有。</v>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="23" t="str">
+        <v>改了表格结构后想确认系统认不认：把新表格导出成 xlsx，让 AI 帮你跑一下包里「工具」文件夹的表单字段自检，它会逐列告诉你认成了什么、有没有认不出来的列。</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A5:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+  </mergeCells>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C27"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -1576,31 +1989,42 @@
         <v>改完程序跑一下，AI 会告诉你怎么跑</v>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="6" t="str">
-        <v>工具 / 发布脚本</v>
+        <v>工具 / 表单字段自检.js</v>
       </c>
       <c r="B11" s="7" t="str">
-        <v>把改好的程序发到内网</v>
+        <v>逐列检查需求表的列系统认不认</v>
       </c>
       <c r="C11" s="7" t="str">
-        <v>改完要上线时用</v>
+        <v>改了需求收集表之后，让 AI 帮你跑</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="8" t="str">
+        <v>工具 / 发布脚本</v>
+      </c>
+      <c r="B12" s="9" t="str">
+        <v>把改好的程序发到内网</v>
+      </c>
+      <c r="C12" s="9" t="str">
+        <v>改完要上线时用</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="6" t="str">
         <v>交接说明.md</v>
       </c>
-      <c r="B12" s="9" t="str">
+      <c r="B13" s="7" t="str">
         <v>文字版的交接说明</v>
       </c>
-      <c r="C12" s="9" t="str">
+      <c r="C13" s="7" t="str">
         <v>想看更详细的背景时</v>
       </c>
     </row>
-    <row r="13" ht="8" customHeight="1"/>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="17" t="str">
+    <row r="14" ht="8" customHeight="1"/>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="17" t="str">
         <v>建议：把这个压缩包在自己的微云或电脑上再存一份。网站长期保留，但备份是自己的事。</v>
       </c>
     </row>
@@ -1608,10 +2032,10 @@
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/排期工具_维护手册.xlsx
+++ b/排期工具_维护手册.xlsx
@@ -1894,7 +1894,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -2002,29 +2002,40 @@
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="8" t="str">
-        <v>工具 / 发布脚本</v>
+        <v>工具 / 其它脚本</v>
       </c>
       <c r="B12" s="9" t="str">
-        <v>把改好的程序发到内网</v>
+        <v>给程序员/AI 用的辅助脚本</v>
       </c>
       <c r="C12" s="9" t="str">
-        <v>改完要上线时用</v>
+        <v>你不用管</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="6" t="str">
+        <v>工具 / 发布脚本</v>
+      </c>
+      <c r="B13" s="7" t="str">
+        <v>把改好的程序发到内网</v>
+      </c>
+      <c r="C13" s="7" t="str">
+        <v>改完要上线时用</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="8" t="str">
         <v>交接说明.md</v>
       </c>
-      <c r="B13" s="7" t="str">
+      <c r="B14" s="9" t="str">
         <v>文字版的交接说明</v>
       </c>
-      <c r="C13" s="7" t="str">
+      <c r="C14" s="9" t="str">
         <v>想看更详细的背景时</v>
       </c>
     </row>
-    <row r="14" ht="8" customHeight="1"/>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="17" t="str">
+    <row r="15" ht="8" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="17" t="str">
         <v>建议：把这个压缩包在自己的微云或电脑上再存一份。网站长期保留，但备份是自己的事。</v>
       </c>
     </row>
@@ -2032,10 +2043,10 @@
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/排期工具_维护手册.xlsx
+++ b/排期工具_维护手册.xlsx
@@ -1894,7 +1894,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -2013,29 +2013,40 @@
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="6" t="str">
-        <v>工具 / 发布脚本</v>
+        <v>AI助手版 / 整个文件夹</v>
       </c>
       <c r="B13" s="7" t="str">
-        <v>把改好的程序发到内网</v>
+        <v>同一套排期规则的另一份实现，可以让 AI 助手在对话里帮你排期</v>
       </c>
       <c r="C13" s="7" t="str">
-        <v>改完要上线时用</v>
+        <v>可选。不想折腾就整个忽略，网页版已经够用</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="8" t="str">
+        <v>工具 / 发布脚本</v>
+      </c>
+      <c r="B14" s="9" t="str">
+        <v>把改好的程序发到内网</v>
+      </c>
+      <c r="C14" s="9" t="str">
+        <v>改完要上线时用</v>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="6" t="str">
         <v>交接说明.md</v>
       </c>
-      <c r="B14" s="9" t="str">
+      <c r="B15" s="7" t="str">
         <v>文字版的交接说明</v>
       </c>
-      <c r="C14" s="9" t="str">
+      <c r="C15" s="7" t="str">
         <v>想看更详细的背景时</v>
       </c>
     </row>
-    <row r="15" ht="8" customHeight="1"/>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="17" t="str">
+    <row r="16" ht="8" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="17" t="str">
         <v>建议：把这个压缩包在自己的微云或电脑上再存一份。网站长期保留，但备份是自己的事。</v>
       </c>
     </row>
@@ -2043,10 +2054,10 @@
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
   </ignoredErrors>
 </worksheet>
 </file>